--- a/Data_clean/MCAS/Estados_US/Edos_USA_2023/MASSACHUSETTS_2023.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2023/MASSACHUSETTS_2023.xlsx
@@ -351,40 +351,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D399"/>
+  <dimension ref="A1:D393"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AGUASCALIENTES</t>
+          <t>Aguascalientes</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AGUASCALIENTES</t>
+          <t>Aguascalientes</t>
         </is>
       </c>
       <c r="C2">
@@ -395,9 +395,14 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C3">
@@ -410,12 +415,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BAJA CALIFORNIA</t>
+          <t>Baja California</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MEXICALI</t>
+          <t>Mexicali</t>
         </is>
       </c>
       <c r="C4">
@@ -426,9 +431,14 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TIJUANA</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="C5">
@@ -439,9 +449,14 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C6">
@@ -454,12 +469,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BAJA CALIFORNIA SUR</t>
+          <t>Baja California Sur</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LOS CABOS</t>
+          <t>Los Cabos</t>
         </is>
       </c>
       <c r="C7">
@@ -470,9 +485,14 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MULEGÉ</t>
+          <t>Mulegé</t>
         </is>
       </c>
       <c r="C8">
@@ -483,9 +503,14 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C9">
@@ -498,12 +523,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CAMPECHE</t>
+          <t>Campeche</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CALKINÍ</t>
+          <t>Calkiní</t>
         </is>
       </c>
       <c r="C10">
@@ -514,9 +539,14 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ESCÁRCEGA</t>
+          <t>Escárcega</t>
         </is>
       </c>
       <c r="C11">
@@ -527,9 +557,14 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C12">
@@ -542,12 +577,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CHIAPAS</t>
+          <t>Chiapas</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ACACOYAGUA</t>
+          <t>Acacoyagua</t>
         </is>
       </c>
       <c r="C13">
@@ -558,9 +593,14 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AMATENANGO DE LA FRONTERA</t>
+          <t>Amatenango De La Frontera</t>
         </is>
       </c>
       <c r="C14">
@@ -571,9 +611,14 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ANGEL ALBINO CORZO</t>
+          <t>Angel Albino Corzo</t>
         </is>
       </c>
       <c r="C15">
@@ -584,9 +629,14 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ARRIAGA</t>
+          <t>Arriaga</t>
         </is>
       </c>
       <c r="C16">
@@ -597,9 +647,14 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BEJUCAL DE OCAMPO</t>
+          <t>Bejucal De Ocampo</t>
         </is>
       </c>
       <c r="C17">
@@ -610,9 +665,14 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BELLA VISTA</t>
+          <t>Bella Vista</t>
         </is>
       </c>
       <c r="C18">
@@ -623,9 +683,14 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BENEMÉRITO DE LAS AMÉRICAS</t>
+          <t>Benemérito De Las Américas</t>
         </is>
       </c>
       <c r="C19">
@@ -636,9 +701,14 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CACAHOATÁN</t>
+          <t>Cacahoatán</t>
         </is>
       </c>
       <c r="C20">
@@ -649,9 +719,14 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CHAMULA</t>
+          <t>Chamula</t>
         </is>
       </c>
       <c r="C21">
@@ -662,9 +737,14 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CHAPULTENANGO</t>
+          <t>Chapultenango</t>
         </is>
       </c>
       <c r="C22">
@@ -675,9 +755,14 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CHICOMUSELO</t>
+          <t>Chicomuselo</t>
         </is>
       </c>
       <c r="C23">
@@ -688,9 +773,14 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CINTALAPA</t>
+          <t>Cintalapa</t>
         </is>
       </c>
       <c r="C24">
@@ -701,9 +791,14 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>COMITÁN DE DOMÍNGUEZ</t>
+          <t>Comitán De Domínguez</t>
         </is>
       </c>
       <c r="C25">
@@ -714,9 +809,14 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EL BOSQUE</t>
+          <t>El Bosque</t>
         </is>
       </c>
       <c r="C26">
@@ -727,9 +827,14 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EL PORVENIR</t>
+          <t>El Porvenir</t>
         </is>
       </c>
       <c r="C27">
@@ -740,9 +845,14 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ESCUINTLA</t>
+          <t>Escuintla</t>
         </is>
       </c>
       <c r="C28">
@@ -753,9 +863,14 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FRONTERA COMALAPA</t>
+          <t>Frontera Comalapa</t>
         </is>
       </c>
       <c r="C29">
@@ -766,9 +881,14 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HUEHUETÁN</t>
+          <t>Huehuetán</t>
         </is>
       </c>
       <c r="C30">
@@ -779,9 +899,14 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HUIXTLA</t>
+          <t>Huixtla</t>
         </is>
       </c>
       <c r="C31">
@@ -792,9 +917,14 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HUIXTÁN</t>
+          <t>Huixtán</t>
         </is>
       </c>
       <c r="C32">
@@ -805,9 +935,14 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JUÁREZ</t>
+          <t>Juárez</t>
         </is>
       </c>
       <c r="C33">
@@ -818,9 +953,14 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LA CONCORDIA</t>
+          <t>La Concordia</t>
         </is>
       </c>
       <c r="C34">
@@ -831,9 +971,14 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LA TRINITARIA</t>
+          <t>La Trinitaria</t>
         </is>
       </c>
       <c r="C35">
@@ -844,9 +989,14 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LAS MARGARITAS</t>
+          <t>Las Margaritas</t>
         </is>
       </c>
       <c r="C36">
@@ -857,9 +1007,14 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MAPASTEPEC</t>
+          <t>Mapastepec</t>
         </is>
       </c>
       <c r="C37">
@@ -870,9 +1025,14 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MAZAPA DE MADERO</t>
+          <t>Mazapa De Madero</t>
         </is>
       </c>
       <c r="C38">
@@ -883,9 +1043,14 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MAZATÁN</t>
+          <t>Mazatán</t>
         </is>
       </c>
       <c r="C39">
@@ -896,9 +1061,14 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MITONTIC</t>
+          <t>Mitontic</t>
         </is>
       </c>
       <c r="C40">
@@ -909,9 +1079,14 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MOTOZINTLA</t>
+          <t>Motozintla</t>
         </is>
       </c>
       <c r="C41">
@@ -922,9 +1097,14 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NO SE REGISTRÓ EL MUNICIPIO/CONDADO/ALCALDÍA DE NACIMIENTO</t>
+          <t>No Se Registró El Municipio/Condado/Alcaldía De Nacimiento</t>
         </is>
       </c>
       <c r="C42">
@@ -935,9 +1115,14 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OCOSINGO</t>
+          <t>Ocosingo</t>
         </is>
       </c>
       <c r="C43">
@@ -948,9 +1133,14 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OXCHUC</t>
+          <t>Oxchuc</t>
         </is>
       </c>
       <c r="C44">
@@ -961,9 +1151,14 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PALENQUE</t>
+          <t>Palenque</t>
         </is>
       </c>
       <c r="C45">
@@ -974,9 +1169,14 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PANTELHÓ</t>
+          <t>Pantelhó</t>
         </is>
       </c>
       <c r="C46">
@@ -987,9 +1187,14 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PANTEPEC</t>
+          <t>Pantepec</t>
         </is>
       </c>
       <c r="C47">
@@ -1000,9 +1205,14 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PICHUCALCO</t>
+          <t>Pichucalco</t>
         </is>
       </c>
       <c r="C48">
@@ -1013,9 +1223,14 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PIJIJIAPAN</t>
+          <t>Pijijiapan</t>
         </is>
       </c>
       <c r="C49">
@@ -1026,9 +1241,14 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>REFORMA</t>
+          <t>Reforma</t>
         </is>
       </c>
       <c r="C50">
@@ -1039,9 +1259,14 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SABANILLA</t>
+          <t>Sabanilla</t>
         </is>
       </c>
       <c r="C51">
@@ -1052,9 +1277,14 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SALTO DE AGUA</t>
+          <t>Salto De Agua</t>
         </is>
       </c>
       <c r="C52">
@@ -1065,9 +1295,14 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SAN CRISTÓBAL DE LAS CASAS</t>
+          <t>San Cristóbal De Las Casas</t>
         </is>
       </c>
       <c r="C53">
@@ -1078,9 +1313,14 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SILTEPEC</t>
+          <t>Siltepec</t>
         </is>
       </c>
       <c r="C54">
@@ -1091,9 +1331,14 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SUCHIATE</t>
+          <t>Suchiate</t>
         </is>
       </c>
       <c r="C55">
@@ -1104,9 +1349,14 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TAPACHULA</t>
+          <t>Tapachula</t>
         </is>
       </c>
       <c r="C56">
@@ -1117,9 +1367,14 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TENEJAPA</t>
+          <t>Tenejapa</t>
         </is>
       </c>
       <c r="C57">
@@ -1130,9 +1385,14 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TEOPISCA</t>
+          <t>Teopisca</t>
         </is>
       </c>
       <c r="C58">
@@ -1143,9 +1403,14 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TUXTLA CHICO</t>
+          <t>Tuxtla Chico</t>
         </is>
       </c>
       <c r="C59">
@@ -1156,9 +1421,14 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TUZANTÁN</t>
+          <t>Tuzantán</t>
         </is>
       </c>
       <c r="C60">
@@ -1169,9 +1439,14 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>UNIÓN JUÁREZ</t>
+          <t>Unión Juárez</t>
         </is>
       </c>
       <c r="C61">
@@ -1182,9 +1457,14 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VILLA COMALTITLÁN</t>
+          <t>Villa Comaltitlán</t>
         </is>
       </c>
       <c r="C62">
@@ -1195,9 +1475,14 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C63">
@@ -1210,12 +1495,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CHIHUAHUA</t>
+          <t>Chihuahua</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CHIHUAHUA</t>
+          <t>Chihuahua</t>
         </is>
       </c>
       <c r="C64">
@@ -1226,9 +1511,14 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HIDALGO DEL PARRAL</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C65">
@@ -1239,9 +1529,14 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C66">
@@ -1254,12 +1549,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CIUDAD DE MÉXICO</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AZCAPOTZALCO</t>
+          <t>Azcapotzalco</t>
         </is>
       </c>
       <c r="C67">
@@ -1270,9 +1565,14 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BENITO JUÁREZ</t>
+          <t>Benito Juárez</t>
         </is>
       </c>
       <c r="C68">
@@ -1283,9 +1583,14 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>COYOACÁN</t>
+          <t>Coyoacán</t>
         </is>
       </c>
       <c r="C69">
@@ -1296,9 +1601,14 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CUAJIMALPA DE MORELOS</t>
+          <t>Cuajimalpa De Morelos</t>
         </is>
       </c>
       <c r="C70">
@@ -1309,9 +1619,14 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CUAUHTÉMOC</t>
+          <t>Cuauhtémoc</t>
         </is>
       </c>
       <c r="C71">
@@ -1322,9 +1637,14 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GUSTAVO A. MADERO</t>
+          <t>Gustavo A. Madero</t>
         </is>
       </c>
       <c r="C72">
@@ -1335,9 +1655,14 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IZTACALCO</t>
+          <t>Iztacalco</t>
         </is>
       </c>
       <c r="C73">
@@ -1348,9 +1673,14 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>IZTAPALAPA</t>
+          <t>Iztapalapa</t>
         </is>
       </c>
       <c r="C74">
@@ -1361,9 +1691,14 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>LA MAGDALENA CONTRERAS</t>
+          <t>La Magdalena Contreras</t>
         </is>
       </c>
       <c r="C75">
@@ -1374,9 +1709,14 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MIGUEL HIDALGO</t>
+          <t>Miguel Hidalgo</t>
         </is>
       </c>
       <c r="C76">
@@ -1387,9 +1727,14 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TLALPAN</t>
+          <t>Tlalpan</t>
         </is>
       </c>
       <c r="C77">
@@ -1400,9 +1745,14 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>VENUSTIANO CARRANZA</t>
+          <t>Venustiano Carranza</t>
         </is>
       </c>
       <c r="C78">
@@ -1413,9 +1763,14 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ÁLVARO OBREGÓN</t>
+          <t>Álvaro Obregón</t>
         </is>
       </c>
       <c r="C79">
@@ -1426,9 +1781,14 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C80">
@@ -1441,12 +1801,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>COAHUILA DE ZARAGOZA</t>
+          <t>Coahuila De Zaragoza</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SABINAS</t>
+          <t>Sabinas</t>
         </is>
       </c>
       <c r="C81">
@@ -1457,9 +1817,14 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Coahuila De Zaragoza</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C82">
@@ -1472,12 +1837,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DURANGO</t>
+          <t>Durango</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NAZAS</t>
+          <t>Nazas</t>
         </is>
       </c>
       <c r="C83">
@@ -1488,9 +1853,14 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SAN JUAN DE GUADALUPE</t>
+          <t>San Juan De Guadalupe</t>
         </is>
       </c>
       <c r="C84">
@@ -1501,9 +1871,14 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C85">
@@ -1516,12 +1891,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ESTADO DE MÉXICO</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ACAMBAY DE RUÍZ CASTAÑEDA</t>
+          <t>Acambay De Ruíz Castañeda</t>
         </is>
       </c>
       <c r="C86">
@@ -1532,9 +1907,14 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AMECAMECA</t>
+          <t>Amecameca</t>
         </is>
       </c>
       <c r="C87">
@@ -1545,9 +1925,14 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ATIZAPÁN DE ZARAGOZA</t>
+          <t>Atizapán De Zaragoza</t>
         </is>
       </c>
       <c r="C88">
@@ -1558,9 +1943,14 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CALIMAYA</t>
+          <t>Calimaya</t>
         </is>
       </c>
       <c r="C89">
@@ -1571,9 +1961,14 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CHIMALHUACÁN</t>
+          <t>Chimalhuacán</t>
         </is>
       </c>
       <c r="C90">
@@ -1584,9 +1979,14 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>COATEPEC HARINAS</t>
+          <t>Coatepec Harinas</t>
         </is>
       </c>
       <c r="C91">
@@ -1597,9 +1997,14 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IXTAPALUCA</t>
+          <t>Ixtapaluca</t>
         </is>
       </c>
       <c r="C92">
@@ -1610,9 +2015,14 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>IXTAPAN DE LA SAL</t>
+          <t>Ixtapan De La Sal</t>
         </is>
       </c>
       <c r="C93">
@@ -1623,9 +2033,14 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JILOTZINGO</t>
+          <t>Jilotzingo</t>
         </is>
       </c>
       <c r="C94">
@@ -1636,9 +2051,14 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LA PAZ</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="C95">
@@ -1649,9 +2069,14 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>NAUCALPAN DE JUÁREZ</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C96">
@@ -1662,9 +2087,14 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>NEZAHUALCÓYOTL</t>
+          <t>Nezahualcóyotl</t>
         </is>
       </c>
       <c r="C97">
@@ -1675,9 +2105,14 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>NICOLÁS ROMERO</t>
+          <t>Nicolás Romero</t>
         </is>
       </c>
       <c r="C98">
@@ -1688,9 +2123,14 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SAN FELIPE DEL PROGRESO</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C99">
@@ -1701,9 +2141,14 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TEMASCALTEPEC</t>
+          <t>Temascaltepec</t>
         </is>
       </c>
       <c r="C100">
@@ -1714,9 +2159,14 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TEMOAYA</t>
+          <t>Temoaya</t>
         </is>
       </c>
       <c r="C101">
@@ -1727,9 +2177,14 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TENANCINGO</t>
+          <t>Tenancingo</t>
         </is>
       </c>
       <c r="C102">
@@ -1740,9 +2195,14 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>TEXCOCO</t>
+          <t>Texcoco</t>
         </is>
       </c>
       <c r="C103">
@@ -1753,9 +2213,14 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA DE BAZ</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C104">
@@ -1766,9 +2231,14 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TOLUCA</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="C105">
@@ -1779,9 +2249,14 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TONATICO</t>
+          <t>Tonatico</t>
         </is>
       </c>
       <c r="C106">
@@ -1792,9 +2267,14 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>VILLA VICTORIA</t>
+          <t>Villa Victoria</t>
         </is>
       </c>
       <c r="C107">
@@ -1805,9 +2285,14 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C108">
@@ -1820,12 +2305,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GUANAJUATO</t>
+          <t>Guanajuato</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>CELAYA</t>
+          <t>Celaya</t>
         </is>
       </c>
       <c r="C109">
@@ -1836,9 +2321,14 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>COMONFORT</t>
+          <t>Comonfort</t>
         </is>
       </c>
       <c r="C110">
@@ -1849,9 +2339,14 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>CORONEO</t>
+          <t>Coroneo</t>
         </is>
       </c>
       <c r="C111">
@@ -1862,9 +2357,14 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DOLORES HIDALGO CUNA DE LA INDEPENDENCIA NACIONAL</t>
+          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
         </is>
       </c>
       <c r="C112">
@@ -1875,9 +2375,14 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>GUANAJUATO</t>
+          <t>Guanajuato</t>
         </is>
       </c>
       <c r="C113">
@@ -1888,9 +2393,14 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>IRAPUATO</t>
+          <t>Irapuato</t>
         </is>
       </c>
       <c r="C114">
@@ -1901,9 +2411,14 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>JERÉCUARO</t>
+          <t>Jerécuaro</t>
         </is>
       </c>
       <c r="C115">
@@ -1914,9 +2429,14 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LEÓN</t>
+          <t>León</t>
         </is>
       </c>
       <c r="C116">
@@ -1927,9 +2447,14 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PÉNJAMO</t>
+          <t>Pénjamo</t>
         </is>
       </c>
       <c r="C117">
@@ -1940,9 +2465,14 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SALAMANCA</t>
+          <t>Salamanca</t>
         </is>
       </c>
       <c r="C118">
@@ -1953,9 +2483,14 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TIERRA BLANCA</t>
+          <t>Tierra Blanca</t>
         </is>
       </c>
       <c r="C119">
@@ -1966,9 +2501,14 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>XICHÚ</t>
+          <t>Xichú</t>
         </is>
       </c>
       <c r="C120">
@@ -1979,9 +2519,14 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C121">
@@ -1994,12 +2539,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ACAPULCO DE JUÁREZ</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C122">
@@ -2010,9 +2555,14 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>AHUACUOTZINGO</t>
+          <t>Ahuacuotzingo</t>
         </is>
       </c>
       <c r="C123">
@@ -2023,9 +2573,14 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>AYUTLA DE LOS LIBRES</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C124">
@@ -2036,9 +2591,14 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>AZOYÚ</t>
+          <t>Azoyú</t>
         </is>
       </c>
       <c r="C125">
@@ -2049,9 +2609,14 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CHILAPA DE ÁLVAREZ</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C126">
@@ -2062,9 +2627,14 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>COPALILLO</t>
+          <t>Copalillo</t>
         </is>
       </c>
       <c r="C127">
@@ -2075,9 +2645,14 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>COPANATOYAC</t>
+          <t>Copanatoyac</t>
         </is>
       </c>
       <c r="C128">
@@ -2088,9 +2663,14 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>COYUCA DE CATALÁN</t>
+          <t>Coyuca De Catalán</t>
         </is>
       </c>
       <c r="C129">
@@ -2101,9 +2681,14 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EDUARDO NERI</t>
+          <t>Eduardo Neri</t>
         </is>
       </c>
       <c r="C130">
@@ -2114,9 +2699,14 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>FLORENCIO VILLARREAL</t>
+          <t>Florencio Villarreal</t>
         </is>
       </c>
       <c r="C131">
@@ -2127,9 +2717,14 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>IGUALAPA</t>
+          <t>Igualapa</t>
         </is>
       </c>
       <c r="C132">
@@ -2140,9 +2735,14 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MALINALTEPEC</t>
+          <t>Malinaltepec</t>
         </is>
       </c>
       <c r="C133">
@@ -2153,9 +2753,14 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MARQUELIA</t>
+          <t>Marquelia</t>
         </is>
       </c>
       <c r="C134">
@@ -2166,9 +2771,14 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>METLATÓNOC</t>
+          <t>Metlatónoc</t>
         </is>
       </c>
       <c r="C135">
@@ -2179,9 +2789,14 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>OMETEPEC</t>
+          <t>Ometepec</t>
         </is>
       </c>
       <c r="C136">
@@ -2192,9 +2807,14 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>QUECHULTENANGO</t>
+          <t>Quechultenango</t>
         </is>
       </c>
       <c r="C137">
@@ -2205,9 +2825,14 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SAN LUIS ACATLÁN</t>
+          <t>San Luis Acatlán</t>
         </is>
       </c>
       <c r="C138">
@@ -2218,9 +2843,14 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SAN MIGUEL TOTOLAPAN</t>
+          <t>San Miguel Totolapan</t>
         </is>
       </c>
       <c r="C139">
@@ -2231,9 +2861,14 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TECOANAPA</t>
+          <t>Tecoanapa</t>
         </is>
       </c>
       <c r="C140">
@@ -2244,9 +2879,14 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>TELOLOAPAN</t>
+          <t>Teloloapan</t>
         </is>
       </c>
       <c r="C141">
@@ -2257,9 +2897,14 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>TLACOACHISTLAHUACA</t>
+          <t>Tlacoachistlahuaca</t>
         </is>
       </c>
       <c r="C142">
@@ -2270,9 +2915,14 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>TLALIXTAQUILLA DE MALDONADO</t>
+          <t>Tlalixtaquilla De Maldonado</t>
         </is>
       </c>
       <c r="C143">
@@ -2283,9 +2933,14 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>TLAPA DE COMONFORT</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C144">
@@ -2296,9 +2951,14 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TÉCPAN DE GALEANA</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C145">
@@ -2309,9 +2969,14 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>XALPATLÁHUAC</t>
+          <t>Xalpatláhuac</t>
         </is>
       </c>
       <c r="C146">
@@ -2322,9 +2987,14 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ZAPOTITLÁN TABLAS</t>
+          <t>Zapotitlán Tablas</t>
         </is>
       </c>
       <c r="C147">
@@ -2335,9 +3005,14 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ZITLALA</t>
+          <t>Zitlala</t>
         </is>
       </c>
       <c r="C148">
@@ -2348,9 +3023,14 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C149">
@@ -2363,12 +3043,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>HIDALGO</t>
+          <t>Hidalgo</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ACTOPAN</t>
+          <t>Actopan</t>
         </is>
       </c>
       <c r="C150">
@@ -2379,9 +3059,14 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ALFAJAYUCAN</t>
+          <t>Alfajayucan</t>
         </is>
       </c>
       <c r="C151">
@@ -2392,9 +3077,14 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ATOTONILCO DE TULA</t>
+          <t>Atotonilco De Tula</t>
         </is>
       </c>
       <c r="C152">
@@ -2405,9 +3095,14 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>FRANCISCO I. MADERO</t>
+          <t>Francisco I. Madero</t>
         </is>
       </c>
       <c r="C153">
@@ -2418,9 +3113,14 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>HUASCA DE OCAMPO</t>
+          <t>Huasca De Ocampo</t>
         </is>
       </c>
       <c r="C154">
@@ -2431,9 +3131,14 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>HUAZALINGO</t>
+          <t>Huazalingo</t>
         </is>
       </c>
       <c r="C155">
@@ -2444,9 +3149,14 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PACHUCA DE SOTO</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C156">
@@ -2457,9 +3167,14 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SAN AGUSTÍN TLAXIACA</t>
+          <t>San Agustín Tlaxiaca</t>
         </is>
       </c>
       <c r="C157">
@@ -2470,9 +3185,14 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>TENANGO DE DORIA</t>
+          <t>Tenango De Doria</t>
         </is>
       </c>
       <c r="C158">
@@ -2483,9 +3203,14 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>TLANCHINOL</t>
+          <t>Tlanchinol</t>
         </is>
       </c>
       <c r="C159">
@@ -2496,9 +3221,14 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>TULA DE ALLENDE</t>
+          <t>Tula De Allende</t>
         </is>
       </c>
       <c r="C160">
@@ -2509,9 +3239,14 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ZIMAPÁN</t>
+          <t>Zimapán</t>
         </is>
       </c>
       <c r="C161">
@@ -2522,9 +3257,14 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C162">
@@ -2537,12 +3277,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>JALISCO</t>
+          <t>Jalisco</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>AUTLÁN DE NAVARRO</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C163">
@@ -2553,9 +3293,14 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>AYOTLÁN</t>
+          <t>Ayotlán</t>
         </is>
       </c>
       <c r="C164">
@@ -2566,9 +3311,14 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>AYUTLA</t>
+          <t>Ayutla</t>
         </is>
       </c>
       <c r="C165">
@@ -2579,9 +3329,14 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>CUAUTITLÁN DE GARCÍA BARRAGÁN</t>
+          <t>Cuautitlán De García Barragán</t>
         </is>
       </c>
       <c r="C166">
@@ -2592,9 +3347,14 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>EL SALTO</t>
+          <t>El Salto</t>
         </is>
       </c>
       <c r="C167">
@@ -2605,9 +3365,14 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ENCARNACIÓN DE DÍAZ</t>
+          <t>Encarnación De Díaz</t>
         </is>
       </c>
       <c r="C168">
@@ -2618,9 +3383,14 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>GUADALAJARA</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="C169">
@@ -2631,9 +3401,14 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>IXTLAHUACÁN DE LOS MEMBRILLOS</t>
+          <t>Ixtlahuacán De Los Membrillos</t>
         </is>
       </c>
       <c r="C170">
@@ -2644,9 +3419,14 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>IXTLAHUACÁN DEL RÍO</t>
+          <t>Ixtlahuacán Del Río</t>
         </is>
       </c>
       <c r="C171">
@@ -2657,9 +3437,14 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>LA HUERTA</t>
+          <t>La Huerta</t>
         </is>
       </c>
       <c r="C172">
@@ -2670,9 +3455,14 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>LA MANZANILLA DE LA PAZ</t>
+          <t>La Manzanilla De La Paz</t>
         </is>
       </c>
       <c r="C173">
@@ -2683,9 +3473,14 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>LAGOS DE MORENO</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C174">
@@ -2696,9 +3491,14 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MAZAMITLA</t>
+          <t>Mazamitla</t>
         </is>
       </c>
       <c r="C175">
@@ -2709,9 +3509,14 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>OCOTLÁN</t>
+          <t>Ocotlán</t>
         </is>
       </c>
       <c r="C176">
@@ -2722,9 +3527,14 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PUERTO VALLARTA</t>
+          <t>Puerto Vallarta</t>
         </is>
       </c>
       <c r="C177">
@@ -2735,9 +3545,14 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="C178">
@@ -2748,9 +3563,14 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SAN MIGUEL EL ALTO</t>
+          <t>San Miguel El Alto</t>
         </is>
       </c>
       <c r="C179">
@@ -2761,9 +3581,14 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SAN PEDRO TLAQUEPAQUE</t>
+          <t>San Pedro Tlaquepaque</t>
         </is>
       </c>
       <c r="C180">
@@ -2774,9 +3599,14 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>TEPATITLÁN DE MORELOS</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C181">
@@ -2787,9 +3617,14 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>TEUCHITLÁN</t>
+          <t>Teuchitlán</t>
         </is>
       </c>
       <c r="C182">
@@ -2800,9 +3635,14 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>TIZAPÁN EL ALTO</t>
+          <t>Tizapán El Alto</t>
         </is>
       </c>
       <c r="C183">
@@ -2813,9 +3653,14 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>TLAJOMULCO DE ZÚÑIGA</t>
+          <t>Tlajomulco De Zúñiga</t>
         </is>
       </c>
       <c r="C184">
@@ -2826,9 +3671,14 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>TUXCACUESCO</t>
+          <t>Tuxcacuesco</t>
         </is>
       </c>
       <c r="C185">
@@ -2839,9 +3689,14 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>TUXCUECA</t>
+          <t>Tuxcueca</t>
         </is>
       </c>
       <c r="C186">
@@ -2852,9 +3707,14 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>UNIÓN DE TULA</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C187">
@@ -2865,9 +3725,14 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ZAPOPAN</t>
+          <t>Zapopan</t>
         </is>
       </c>
       <c r="C188">
@@ -2878,9 +3743,14 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ZAPOTLÁN EL GRANDE</t>
+          <t>Zapotlán El Grande</t>
         </is>
       </c>
       <c r="C189">
@@ -2891,9 +3761,14 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C190">
@@ -2906,12 +3781,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>MICHOACÁN DE OCAMPO</t>
+          <t>Michoacán De Ocampo</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>CHINICUILA</t>
+          <t>Chinicuila</t>
         </is>
       </c>
       <c r="C191">
@@ -2922,9 +3797,14 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>EPITACIO HUERTA</t>
+          <t>Epitacio Huerta</t>
         </is>
       </c>
       <c r="C192">
@@ -2935,9 +3815,14 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>HIDALGO</t>
+          <t>Hidalgo</t>
         </is>
       </c>
       <c r="C193">
@@ -2948,9 +3833,14 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>HUANDACAREO</t>
+          <t>Huandacareo</t>
         </is>
       </c>
       <c r="C194">
@@ -2961,9 +3851,14 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>JUNGAPEO</t>
+          <t>Jungapeo</t>
         </is>
       </c>
       <c r="C195">
@@ -2974,9 +3869,14 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>MORELIA</t>
+          <t>Morelia</t>
         </is>
       </c>
       <c r="C196">
@@ -2987,9 +3887,14 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>MÚGICA</t>
+          <t>Múgica</t>
         </is>
       </c>
       <c r="C197">
@@ -3000,9 +3905,14 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PAJACUARÁN</t>
+          <t>Pajacuarán</t>
         </is>
       </c>
       <c r="C198">
@@ -3013,9 +3923,14 @@
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PURUÁNDIRO</t>
+          <t>Puruándiro</t>
         </is>
       </c>
       <c r="C199">
@@ -3026,9 +3941,14 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PÁTZCUARO</t>
+          <t>Pátzcuaro</t>
         </is>
       </c>
       <c r="C200">
@@ -3039,9 +3959,14 @@
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>QUIROGA</t>
+          <t>Quiroga</t>
         </is>
       </c>
       <c r="C201">
@@ -3052,9 +3977,14 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>TOCUMBO</t>
+          <t>Tocumbo</t>
         </is>
       </c>
       <c r="C202">
@@ -3065,9 +3995,14 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>TUXPAN</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C203">
@@ -3078,9 +4013,14 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>URUAPAN</t>
+          <t>Uruapan</t>
         </is>
       </c>
       <c r="C204">
@@ -3091,9 +4031,14 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>VENUSTIANO CARRANZA</t>
+          <t>Venustiano Carranza</t>
         </is>
       </c>
       <c r="C205">
@@ -3104,9 +4049,14 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ZACAPU</t>
+          <t>Zacapu</t>
         </is>
       </c>
       <c r="C206">
@@ -3117,9 +4067,14 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ZIRACUARETIRO</t>
+          <t>Ziracuaretiro</t>
         </is>
       </c>
       <c r="C207">
@@ -3130,9 +4085,14 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C208">
@@ -3145,12 +4105,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>MORELOS</t>
+          <t>Morelos</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>CUERNAVACA</t>
+          <t>Cuernavaca</t>
         </is>
       </c>
       <c r="C209">
@@ -3161,9 +4121,14 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>TEMIXCO</t>
+          <t>Temixco</t>
         </is>
       </c>
       <c r="C210">
@@ -3174,9 +4139,14 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>TETELA DEL VOLCÁN</t>
+          <t>Tetela Del Volcán</t>
         </is>
       </c>
       <c r="C211">
@@ -3187,9 +4157,14 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>TLAQUILTENANGO</t>
+          <t>Tlaquiltenango</t>
         </is>
       </c>
       <c r="C212">
@@ -3200,9 +4175,14 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C213">
@@ -3215,12 +4195,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>NAYARIT</t>
+          <t>Nayarit</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>TEPIC</t>
+          <t>Tepic</t>
         </is>
       </c>
       <c r="C214">
@@ -3231,9 +4211,14 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C215">
@@ -3246,12 +4231,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>NUEVO LEÓN</t>
+          <t>Nuevo León</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>ANÁHUAC</t>
+          <t>Anáhuac</t>
         </is>
       </c>
       <c r="C216">
@@ -3262,9 +4247,14 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MONTERREY</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="C217">
@@ -3275,9 +4265,14 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C218">
@@ -3290,12 +4285,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>OAXACA</t>
+          <t>Oaxaca</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>ASUNCIÓN IXTALTEPEC</t>
+          <t>Asunción Ixtaltepec</t>
         </is>
       </c>
       <c r="C219">
@@ -3306,9 +4301,14 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>CANDELARIA LOXICHA</t>
+          <t>Candelaria Loxicha</t>
         </is>
       </c>
       <c r="C220">
@@ -3319,9 +4319,14 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>COICOYÁN DE LAS FLORES</t>
+          <t>Coicoyán De Las Flores</t>
         </is>
       </c>
       <c r="C221">
@@ -3332,9 +4337,14 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>COSOLAPA</t>
+          <t>Cosolapa</t>
         </is>
       </c>
       <c r="C222">
@@ -3345,9 +4355,14 @@
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>HEROICA CIUDAD DE JUCHITÁN DE ZARAGOZA</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C223">
@@ -3358,9 +4373,14 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>HUAJUAPAN DE LEÓN</t>
+          <t>Huajuapan De León</t>
         </is>
       </c>
       <c r="C224">
@@ -3371,9 +4391,14 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>LOMA BONITA</t>
+          <t>Loma Bonita</t>
         </is>
       </c>
       <c r="C225">
@@ -3384,9 +4409,14 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>MATÍAS ROMERO AVENDAÑO</t>
+          <t>Matías Romero Avendaño</t>
         </is>
       </c>
       <c r="C226">
@@ -3397,9 +4427,14 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>OAXACA DE JUÁREZ</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C227">
@@ -3410,9 +4445,14 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>SAN AGUSTÍN YATARENI</t>
+          <t>San Agustín Yatareni</t>
         </is>
       </c>
       <c r="C228">
@@ -3423,9 +4463,14 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>SAN ANDRÉS CABECERA NUEVA</t>
+          <t>San Andrés Cabecera Nueva</t>
         </is>
       </c>
       <c r="C229">
@@ -3436,9 +4481,14 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>SAN ANTONINO MONTE VERDE</t>
+          <t>San Antonino Monte Verde</t>
         </is>
       </c>
       <c r="C230">
@@ -3449,9 +4499,14 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>SAN ANTONIO HUITEPEC</t>
+          <t>San Antonio Huitepec</t>
         </is>
       </c>
       <c r="C231">
@@ -3462,9 +4517,14 @@
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>SAN DIONISIO DEL MAR</t>
+          <t>San Dionisio Del Mar</t>
         </is>
       </c>
       <c r="C232">
@@ -3475,9 +4535,14 @@
       </c>
     </row>
     <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>SAN JUAN LACHAO</t>
+          <t>San Juan Lachao</t>
         </is>
       </c>
       <c r="C233">
@@ -3488,9 +4553,14 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>SAN JUAN LALANA</t>
+          <t>San Juan Lalana</t>
         </is>
       </c>
       <c r="C234">
@@ -3501,9 +4571,14 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>SAN JUAN MAZATLÁN</t>
+          <t>San Juan Mazatlán</t>
         </is>
       </c>
       <c r="C235">
@@ -3514,9 +4589,14 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>SAN MARTÍN ZACATEPEC</t>
+          <t>San Martín Zacatepec</t>
         </is>
       </c>
       <c r="C236">
@@ -3527,9 +4607,14 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>SAN MIGUEL EJUTLA</t>
+          <t>San Miguel Ejutla</t>
         </is>
       </c>
       <c r="C237">
@@ -3540,9 +4625,14 @@
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>SAN MIGUEL TULANCINGO</t>
+          <t>San Miguel Tulancingo</t>
         </is>
       </c>
       <c r="C238">
@@ -3553,9 +4643,14 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>SAN PEDRO MIXTEPEC -DTO. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C239">
@@ -3566,9 +4661,14 @@
       </c>
     </row>
     <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>SAN PEDRO Y SAN PABLO TEPOSCOLULA</t>
+          <t>San Pedro Y San Pablo Teposcolula</t>
         </is>
       </c>
       <c r="C240">
@@ -3579,9 +4679,14 @@
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>SANTA CRUZ ZENZONTEPEC</t>
+          <t>Santa Cruz Zenzontepec</t>
         </is>
       </c>
       <c r="C241">
@@ -3592,9 +4697,14 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>SANTA LUCÍA DEL CAMINO</t>
+          <t>Santa Lucía Del Camino</t>
         </is>
       </c>
       <c r="C242">
@@ -3605,9 +4715,14 @@
       </c>
     </row>
     <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>SANTA MARÍA APAZCO</t>
+          <t>Santa María Apazco</t>
         </is>
       </c>
       <c r="C243">
@@ -3618,9 +4733,14 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>SANTA MARÍA HUATULCO</t>
+          <t>Santa María Huatulco</t>
         </is>
       </c>
       <c r="C244">
@@ -3631,9 +4751,14 @@
       </c>
     </row>
     <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>SANTIAGO CHAZUMBA</t>
+          <t>Santiago Chazumba</t>
         </is>
       </c>
       <c r="C245">
@@ -3644,9 +4769,14 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>SANTIAGO JOCOTEPEC</t>
+          <t>Santiago Jocotepec</t>
         </is>
       </c>
       <c r="C246">
@@ -3657,9 +4787,14 @@
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>SANTIAGO PINOTEPA NACIONAL</t>
+          <t>Santiago Pinotepa Nacional</t>
         </is>
       </c>
       <c r="C247">
@@ -3670,9 +4805,14 @@
       </c>
     </row>
     <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO DE MORELOS</t>
+          <t>Santo Domingo De Morelos</t>
         </is>
       </c>
       <c r="C248">
@@ -3683,9 +4823,14 @@
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO TOMALTEPEC</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C249">
@@ -3696,9 +4841,14 @@
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>SANTOS REYES NOPALA</t>
+          <t>Santos Reyes Nopala</t>
         </is>
       </c>
       <c r="C250">
@@ -3709,9 +4859,14 @@
       </c>
     </row>
     <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>TLACOLULA DE MATAMOROS</t>
+          <t>Tlacolula De Matamoros</t>
         </is>
       </c>
       <c r="C251">
@@ -3722,9 +4877,14 @@
       </c>
     </row>
     <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>TOTONTEPEC VILLA DE MORELOS</t>
+          <t>Totontepec Villa De Morelos</t>
         </is>
       </c>
       <c r="C252">
@@ -3735,9 +4895,14 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>VILLA DE TUTUTEPEC DE MELCHOR OCAMPO</t>
+          <t>Villa De Tututepec De Melchor Ocampo</t>
         </is>
       </c>
       <c r="C253">
@@ -3748,9 +4913,14 @@
       </c>
     </row>
     <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>ZAPOTITLÁN LAGUNAS</t>
+          <t>Zapotitlán Lagunas</t>
         </is>
       </c>
       <c r="C254">
@@ -3761,9 +4931,14 @@
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C255">
@@ -3776,12 +4951,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>PUEBLA</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>ACATLÁN</t>
+          <t>Acatlán</t>
         </is>
       </c>
       <c r="C256">
@@ -3792,9 +4967,14 @@
       </c>
     </row>
     <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>AJALPAN</t>
+          <t>Ajalpan</t>
         </is>
       </c>
       <c r="C257">
@@ -3805,9 +4985,14 @@
       </c>
     </row>
     <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>AQUIXTLA</t>
+          <t>Aquixtla</t>
         </is>
       </c>
       <c r="C258">
@@ -3818,9 +5003,14 @@
       </c>
     </row>
     <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>ATEMPAN</t>
+          <t>Atempan</t>
         </is>
       </c>
       <c r="C259">
@@ -3831,9 +5021,14 @@
       </c>
     </row>
     <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>ATLIXCO</t>
+          <t>Atlixco</t>
         </is>
       </c>
       <c r="C260">
@@ -3844,9 +5039,14 @@
       </c>
     </row>
     <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>CALTEPEC</t>
+          <t>Caltepec</t>
         </is>
       </c>
       <c r="C261">
@@ -3857,9 +5057,14 @@
       </c>
     </row>
     <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>CHALCHICOMULA DE SESMA</t>
+          <t>Chalchicomula De Sesma</t>
         </is>
       </c>
       <c r="C262">
@@ -3870,9 +5075,14 @@
       </c>
     </row>
     <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>CHIAUTZINGO</t>
+          <t>Chiautzingo</t>
         </is>
       </c>
       <c r="C263">
@@ -3883,9 +5093,14 @@
       </c>
     </row>
     <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>CHICHIQUILA</t>
+          <t>Chichiquila</t>
         </is>
       </c>
       <c r="C264">
@@ -3896,9 +5111,14 @@
       </c>
     </row>
     <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>CHICONCUAUTLA</t>
+          <t>Chiconcuautla</t>
         </is>
       </c>
       <c r="C265">
@@ -3909,9 +5129,14 @@
       </c>
     </row>
     <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>CHIETLA</t>
+          <t>Chietla</t>
         </is>
       </c>
       <c r="C266">
@@ -3922,9 +5147,14 @@
       </c>
     </row>
     <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>CHIGNAHUAPAN</t>
+          <t>Chignahuapan</t>
         </is>
       </c>
       <c r="C267">
@@ -3935,9 +5165,14 @@
       </c>
     </row>
     <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>CHINANTLA</t>
+          <t>Chinantla</t>
         </is>
       </c>
       <c r="C268">
@@ -3948,9 +5183,14 @@
       </c>
     </row>
     <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>EPATLÁN</t>
+          <t>Epatlán</t>
         </is>
       </c>
       <c r="C269">
@@ -3961,9 +5201,14 @@
       </c>
     </row>
     <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>HERMENEGILDO GALEANA</t>
+          <t>Hermenegildo Galeana</t>
         </is>
       </c>
       <c r="C270">
@@ -3974,9 +5219,14 @@
       </c>
     </row>
     <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>HUAUCHINANGO</t>
+          <t>Huauchinango</t>
         </is>
       </c>
       <c r="C271">
@@ -3987,9 +5237,14 @@
       </c>
     </row>
     <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>HUEHUETLA</t>
+          <t>Huehuetla</t>
         </is>
       </c>
       <c r="C272">
@@ -4000,9 +5255,14 @@
       </c>
     </row>
     <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>HUEHUETLÁN EL GRANDE</t>
+          <t>Huehuetlán El Grande</t>
         </is>
       </c>
       <c r="C273">
@@ -4013,9 +5273,14 @@
       </c>
     </row>
     <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>HUEJOTZINGO</t>
+          <t>Huejotzingo</t>
         </is>
       </c>
       <c r="C274">
@@ -4026,9 +5291,14 @@
       </c>
     </row>
     <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>IXCAQUIXTLA</t>
+          <t>Ixcaquixtla</t>
         </is>
       </c>
       <c r="C275">
@@ -4039,9 +5309,14 @@
       </c>
     </row>
     <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>IXTACAMAXTITLÁN</t>
+          <t>Ixtacamaxtitlán</t>
         </is>
       </c>
       <c r="C276">
@@ -4052,9 +5327,14 @@
       </c>
     </row>
     <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>IZÚCAR DE MATAMOROS</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C277">
@@ -4065,9 +5345,14 @@
       </c>
     </row>
     <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>JUAN N. MÉNDEZ</t>
+          <t>Juan N. Méndez</t>
         </is>
       </c>
       <c r="C278">
@@ -4078,9 +5363,14 @@
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>NEALTICAN</t>
+          <t>Nealtican</t>
         </is>
       </c>
       <c r="C279">
@@ -4091,9 +5381,14 @@
       </c>
     </row>
     <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>PUEBLA</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="C280">
@@ -4104,9 +5399,14 @@
       </c>
     </row>
     <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>SAN ANDRÉS CHOLULA</t>
+          <t>San Andrés Cholula</t>
         </is>
       </c>
       <c r="C281">
@@ -4117,9 +5417,14 @@
       </c>
     </row>
     <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>SAN MARTÍN TEXMELUCAN</t>
+          <t>San Martín Texmelucan</t>
         </is>
       </c>
       <c r="C282">
@@ -4130,9 +5435,14 @@
       </c>
     </row>
     <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>SAN MATÍAS TLALANCALECA</t>
+          <t>San Matías Tlalancaleca</t>
         </is>
       </c>
       <c r="C283">
@@ -4143,9 +5453,14 @@
       </c>
     </row>
     <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>SAN PABLO ANICANO</t>
+          <t>San Pablo Anicano</t>
         </is>
       </c>
       <c r="C284">
@@ -4156,9 +5471,14 @@
       </c>
     </row>
     <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>SAN PEDRO YELOIXTLAHUACA</t>
+          <t>San Pedro Yeloixtlahuaca</t>
         </is>
       </c>
       <c r="C285">
@@ -4169,9 +5489,14 @@
       </c>
     </row>
     <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>SAN SALVADOR EL SECO</t>
+          <t>San Salvador El Seco</t>
         </is>
       </c>
       <c r="C286">
@@ -4182,9 +5507,14 @@
       </c>
     </row>
     <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>SAN SALVADOR EL VERDE</t>
+          <t>San Salvador El Verde</t>
         </is>
       </c>
       <c r="C287">
@@ -4195,9 +5525,14 @@
       </c>
     </row>
     <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>SANTA ISABEL CHOLULA</t>
+          <t>Santa Isabel Cholula</t>
         </is>
       </c>
       <c r="C288">
@@ -4208,9 +5543,14 @@
       </c>
     </row>
     <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>TEPEXCO</t>
+          <t>Tepexco</t>
         </is>
       </c>
       <c r="C289">
@@ -4221,9 +5561,14 @@
       </c>
     </row>
     <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>TILAPA</t>
+          <t>Tilapa</t>
         </is>
       </c>
       <c r="C290">
@@ -4234,9 +5579,14 @@
       </c>
     </row>
     <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>TLAHUAPAN</t>
+          <t>Tlahuapan</t>
         </is>
       </c>
       <c r="C291">
@@ -4247,9 +5597,14 @@
       </c>
     </row>
     <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>TLAPANALÁ</t>
+          <t>Tlapanalá</t>
         </is>
       </c>
       <c r="C292">
@@ -4260,9 +5615,14 @@
       </c>
     </row>
     <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>TLATLAUQUITEPEC</t>
+          <t>Tlatlauquitepec</t>
         </is>
       </c>
       <c r="C293">
@@ -4273,9 +5633,14 @@
       </c>
     </row>
     <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>ZACAPOAXTLA</t>
+          <t>Zacapoaxtla</t>
         </is>
       </c>
       <c r="C294">
@@ -4286,9 +5651,14 @@
       </c>
     </row>
     <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>ZACATLÁN</t>
+          <t>Zacatlán</t>
         </is>
       </c>
       <c r="C295">
@@ -4299,9 +5669,14 @@
       </c>
     </row>
     <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>ZAPOTITLÁN</t>
+          <t>Zapotitlán</t>
         </is>
       </c>
       <c r="C296">
@@ -4312,9 +5687,14 @@
       </c>
     </row>
     <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C297">
@@ -4327,12 +5707,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>QUERÉTARO</t>
+          <t>Querétaro</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>AMEALCO DE BONFIL</t>
+          <t>Amealco De Bonfil</t>
         </is>
       </c>
       <c r="C298">
@@ -4343,9 +5723,14 @@
       </c>
     </row>
     <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>ARROYO SECO</t>
+          <t>Arroyo Seco</t>
         </is>
       </c>
       <c r="C299">
@@ -4356,9 +5741,14 @@
       </c>
     </row>
     <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EL MARQUÉS</t>
+          <t>El Marqués</t>
         </is>
       </c>
       <c r="C300">
@@ -4369,9 +5759,14 @@
       </c>
     </row>
     <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>QUERÉTARO</t>
+          <t>Querétaro</t>
         </is>
       </c>
       <c r="C301">
@@ -4382,9 +5777,14 @@
       </c>
     </row>
     <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C302">
@@ -4397,12 +5797,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>QUINTANA ROO</t>
+          <t>Quintana Roo</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>OTHÓN P. BLANCO</t>
+          <t>Othón P. Blanco</t>
         </is>
       </c>
       <c r="C303">
@@ -4413,9 +5813,14 @@
       </c>
     </row>
     <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C304">
@@ -4428,12 +5833,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>SAN LUIS POTOSÍ</t>
+          <t>San Luis Potosí</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>AHUALULCO</t>
+          <t>Ahualulco</t>
         </is>
       </c>
       <c r="C305">
@@ -4444,9 +5849,14 @@
       </c>
     </row>
     <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>CIUDAD VALLES</t>
+          <t>Ciudad Valles</t>
         </is>
       </c>
       <c r="C306">
@@ -4457,9 +5867,14 @@
       </c>
     </row>
     <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>MATEHUALA</t>
+          <t>Matehuala</t>
         </is>
       </c>
       <c r="C307">
@@ -4470,9 +5885,14 @@
       </c>
     </row>
     <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>RIOVERDE</t>
+          <t>Rioverde</t>
         </is>
       </c>
       <c r="C308">
@@ -4483,9 +5903,14 @@
       </c>
     </row>
     <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>SALINAS</t>
+          <t>Salinas</t>
         </is>
       </c>
       <c r="C309">
@@ -4496,9 +5921,14 @@
       </c>
     </row>
     <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>SAN LUIS POTOSÍ</t>
+          <t>San Luis Potosí</t>
         </is>
       </c>
       <c r="C310">
@@ -4509,9 +5939,14 @@
       </c>
     </row>
     <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>VANEGAS</t>
+          <t>Vanegas</t>
         </is>
       </c>
       <c r="C311">
@@ -4522,9 +5957,14 @@
       </c>
     </row>
     <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>VILLA DE GUADALUPE</t>
+          <t>Villa De Guadalupe</t>
         </is>
       </c>
       <c r="C312">
@@ -4535,9 +5975,14 @@
       </c>
     </row>
     <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>VILLA DE REYES</t>
+          <t>Villa De Reyes</t>
         </is>
       </c>
       <c r="C313">
@@ -4548,9 +5993,14 @@
       </c>
     </row>
     <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C314">
@@ -4563,12 +6013,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>SINALOA</t>
+          <t>Sinaloa</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>AHOME</t>
+          <t>Ahome</t>
         </is>
       </c>
       <c r="C315">
@@ -4579,9 +6029,14 @@
       </c>
     </row>
     <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>CULIACÁN</t>
+          <t>Culiacán</t>
         </is>
       </c>
       <c r="C316">
@@ -4592,9 +6047,14 @@
       </c>
     </row>
     <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>GUASAVE</t>
+          <t>Guasave</t>
         </is>
       </c>
       <c r="C317">
@@ -4605,9 +6065,14 @@
       </c>
     </row>
     <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C318">
@@ -4620,12 +6085,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>SONORA</t>
+          <t>Sonora</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>CAJEME</t>
+          <t>Cajeme</t>
         </is>
       </c>
       <c r="C319">
@@ -4636,9 +6101,14 @@
       </c>
     </row>
     <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>HERMOSILLO</t>
+          <t>Hermosillo</t>
         </is>
       </c>
       <c r="C320">
@@ -4649,9 +6119,14 @@
       </c>
     </row>
     <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>NOGALES</t>
+          <t>Nogales</t>
         </is>
       </c>
       <c r="C321">
@@ -4662,9 +6137,14 @@
       </c>
     </row>
     <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>SAHUARIPA</t>
+          <t>Sahuaripa</t>
         </is>
       </c>
       <c r="C322">
@@ -4675,9 +6155,14 @@
       </c>
     </row>
     <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C323">
@@ -4690,12 +6175,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>TABASCO</t>
+          <t>Tabasco</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>BALANCÁN</t>
+          <t>Balancán</t>
         </is>
       </c>
       <c r="C324">
@@ -4706,9 +6191,14 @@
       </c>
     </row>
     <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="C325">
@@ -4719,9 +6209,14 @@
       </c>
     </row>
     <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>CÁRDENAS</t>
+          <t>Cárdenas</t>
         </is>
       </c>
       <c r="C326">
@@ -4732,9 +6227,14 @@
       </c>
     </row>
     <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>JALPA DE MÉNDEZ</t>
+          <t>Jalpa De Méndez</t>
         </is>
       </c>
       <c r="C327">
@@ -4745,9 +6245,14 @@
       </c>
     </row>
     <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C328">
@@ -4760,12 +6265,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>TAMAULIPAS</t>
+          <t>Tamaulipas</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>CIUDAD MADERO</t>
+          <t>Ciudad Madero</t>
         </is>
       </c>
       <c r="C329">
@@ -4776,9 +6281,14 @@
       </c>
     </row>
     <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>EL MANTE</t>
+          <t>El Mante</t>
         </is>
       </c>
       <c r="C330">
@@ -4789,9 +6299,14 @@
       </c>
     </row>
     <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>GONZÁLEZ</t>
+          <t>González</t>
         </is>
       </c>
       <c r="C331">
@@ -4802,9 +6317,14 @@
       </c>
     </row>
     <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>MATAMOROS</t>
+          <t>Matamoros</t>
         </is>
       </c>
       <c r="C332">
@@ -4815,9 +6335,14 @@
       </c>
     </row>
     <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>REYNOSA</t>
+          <t>Reynosa</t>
         </is>
       </c>
       <c r="C333">
@@ -4828,9 +6353,14 @@
       </c>
     </row>
     <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>TAMPICO</t>
+          <t>Tampico</t>
         </is>
       </c>
       <c r="C334">
@@ -4841,9 +6371,14 @@
       </c>
     </row>
     <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C335">
@@ -4856,12 +6391,12 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>TLAXCALA</t>
+          <t>Tlaxcala</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>ACUAMANALA DE MIGUEL HIDALGO</t>
+          <t>Acuamanala De Miguel Hidalgo</t>
         </is>
       </c>
       <c r="C336">
@@ -4872,9 +6407,14 @@
       </c>
     </row>
     <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>CHIAUTEMPAN</t>
+          <t>Chiautempan</t>
         </is>
       </c>
       <c r="C337">
@@ -4885,9 +6425,14 @@
       </c>
     </row>
     <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>EL CARMEN TEQUEXQUITLA</t>
+          <t>El Carmen Tequexquitla</t>
         </is>
       </c>
       <c r="C338">
@@ -4898,9 +6443,14 @@
       </c>
     </row>
     <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>NATÍVITAS</t>
+          <t>Natívitas</t>
         </is>
       </c>
       <c r="C339">
@@ -4911,9 +6461,14 @@
       </c>
     </row>
     <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>SANCTÓRUM DE LÁZARO CÁRDENAS</t>
+          <t>Sanctórum De Lázaro Cárdenas</t>
         </is>
       </c>
       <c r="C340">
@@ -4924,9 +6479,14 @@
       </c>
     </row>
     <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>TETLATLAHUCA</t>
+          <t>Tetlatlahuca</t>
         </is>
       </c>
       <c r="C341">
@@ -4937,9 +6497,14 @@
       </c>
     </row>
     <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>TLAXCALA</t>
+          <t>Tlaxcala</t>
         </is>
       </c>
       <c r="C342">
@@ -4950,9 +6515,14 @@
       </c>
     </row>
     <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C343">
@@ -4965,12 +6535,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
+          <t>Veracruz De Ignacio De La Llave</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ALPATLÁHUAC</t>
+          <t>Alpatláhuac</t>
         </is>
       </c>
       <c r="C344">
@@ -4981,9 +6551,14 @@
       </c>
     </row>
     <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ALVARADO</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="C345">
@@ -4994,9 +6569,14 @@
       </c>
     </row>
     <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>CALCAHUALCO</t>
+          <t>Calcahualco</t>
         </is>
       </c>
       <c r="C346">
@@ -5007,9 +6587,14 @@
       </c>
     </row>
     <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>CAMARÓN DE TEJEDA</t>
+          <t>Camarón De Tejeda</t>
         </is>
       </c>
       <c r="C347">
@@ -5020,9 +6605,14 @@
       </c>
     </row>
     <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>CASTILLO DE TEAYO</t>
+          <t>Castillo De Teayo</t>
         </is>
       </c>
       <c r="C348">
@@ -5033,9 +6623,14 @@
       </c>
     </row>
     <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>CHUMATLÁN</t>
+          <t>Chumatlán</t>
         </is>
       </c>
       <c r="C349">
@@ -5046,9 +6641,14 @@
       </c>
     </row>
     <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>COATZACOALCOS</t>
+          <t>Coatzacoalcos</t>
         </is>
       </c>
       <c r="C350">
@@ -5059,9 +6659,14 @@
       </c>
     </row>
     <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>COSCOMATEPEC</t>
+          <t>Coscomatepec</t>
         </is>
       </c>
       <c r="C351">
@@ -5072,9 +6677,14 @@
       </c>
     </row>
     <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>CÓRDOBA</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="C352">
@@ -5085,9 +6695,14 @@
       </c>
     </row>
     <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>ESPINAL</t>
+          <t>Espinal</t>
         </is>
       </c>
       <c r="C353">
@@ -5098,9 +6713,14 @@
       </c>
     </row>
     <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>HUATUSCO</t>
+          <t>Huatusco</t>
         </is>
       </c>
       <c r="C354">
@@ -5111,9 +6731,14 @@
       </c>
     </row>
     <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>HUEYAPAN DE OCAMPO</t>
+          <t>Hueyapan De Ocampo</t>
         </is>
       </c>
       <c r="C355">
@@ -5124,9 +6749,14 @@
       </c>
     </row>
     <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>IGNACIO DE LA LLAVE</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C356">
@@ -5137,9 +6767,14 @@
       </c>
     </row>
     <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>IXTACZOQUITLÁN</t>
+          <t>Ixtaczoquitlán</t>
         </is>
       </c>
       <c r="C357">
@@ -5150,9 +6785,14 @@
       </c>
     </row>
     <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>JALACINGO</t>
+          <t>Jalacingo</t>
         </is>
       </c>
       <c r="C358">
@@ -5163,9 +6803,14 @@
       </c>
     </row>
     <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>JOSÉ AZUETA</t>
+          <t>José Azueta</t>
         </is>
       </c>
       <c r="C359">
@@ -5176,9 +6821,14 @@
       </c>
     </row>
     <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>LAS CHOAPAS</t>
+          <t>Las Choapas</t>
         </is>
       </c>
       <c r="C360">
@@ -5189,9 +6839,14 @@
       </c>
     </row>
     <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>MANLIO FABIO ALTAMIRANO</t>
+          <t>Manlio Fabio Altamirano</t>
         </is>
       </c>
       <c r="C361">
@@ -5202,9 +6857,14 @@
       </c>
     </row>
     <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>MARTÍNEZ DE LA TORRE</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C362">
@@ -5215,9 +6875,14 @@
       </c>
     </row>
     <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MECAYAPAN</t>
+          <t>Mecayapan</t>
         </is>
       </c>
       <c r="C363">
@@ -5228,9 +6893,14 @@
       </c>
     </row>
     <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MINATITLÁN</t>
+          <t>Minatitlán</t>
         </is>
       </c>
       <c r="C364">
@@ -5241,9 +6911,14 @@
       </c>
     </row>
     <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>OMEALCA</t>
+          <t>Omealca</t>
         </is>
       </c>
       <c r="C365">
@@ -5254,9 +6929,14 @@
       </c>
     </row>
     <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>ORIZABA</t>
+          <t>Orizaba</t>
         </is>
       </c>
       <c r="C366">
@@ -5267,9 +6947,14 @@
       </c>
     </row>
     <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>PAPANTLA</t>
+          <t>Papantla</t>
         </is>
       </c>
       <c r="C367">
@@ -5280,9 +6965,14 @@
       </c>
     </row>
     <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>PASO DE OVEJAS</t>
+          <t>Paso De Ovejas</t>
         </is>
       </c>
       <c r="C368">
@@ -5293,9 +6983,14 @@
       </c>
     </row>
     <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>POZA RICA DE HIDALGO</t>
+          <t>Poza Rica De Hidalgo</t>
         </is>
       </c>
       <c r="C369">
@@ -5306,9 +7001,14 @@
       </c>
     </row>
     <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>SAN ANDRÉS TUXTLA</t>
+          <t>San Andrés Tuxtla</t>
         </is>
       </c>
       <c r="C370">
@@ -5319,9 +7019,14 @@
       </c>
     </row>
     <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>SAYULA DE ALEMÁN</t>
+          <t>Sayula De Alemán</t>
         </is>
       </c>
       <c r="C371">
@@ -5332,9 +7037,14 @@
       </c>
     </row>
     <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>SOLEDAD DE DOBLADO</t>
+          <t>Soledad De Doblado</t>
         </is>
       </c>
       <c r="C372">
@@ -5345,9 +7055,14 @@
       </c>
     </row>
     <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>TAMIAHUA</t>
+          <t>Tamiahua</t>
         </is>
       </c>
       <c r="C373">
@@ -5358,9 +7073,14 @@
       </c>
     </row>
     <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>TANTOYUCA</t>
+          <t>Tantoyuca</t>
         </is>
       </c>
       <c r="C374">
@@ -5371,9 +7091,14 @@
       </c>
     </row>
     <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>TEXCATEPEC</t>
+          <t>Texcatepec</t>
         </is>
       </c>
       <c r="C375">
@@ -5384,9 +7109,14 @@
       </c>
     </row>
     <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>TIERRA BLANCA</t>
+          <t>Tierra Blanca</t>
         </is>
       </c>
       <c r="C376">
@@ -5397,9 +7127,14 @@
       </c>
     </row>
     <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>TLACOTALPAN</t>
+          <t>Tlacotalpan</t>
         </is>
       </c>
       <c r="C377">
@@ -5410,9 +7145,14 @@
       </c>
     </row>
     <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>TLALIXCOYAN</t>
+          <t>Tlalixcoyan</t>
         </is>
       </c>
       <c r="C378">
@@ -5423,9 +7163,14 @@
       </c>
     </row>
     <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>TUXPAN</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C379">
@@ -5436,9 +7181,14 @@
       </c>
     </row>
     <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>VERACRUZ</t>
+          <t>Veracruz</t>
         </is>
       </c>
       <c r="C380">
@@ -5449,9 +7199,14 @@
       </c>
     </row>
     <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>XALAPA</t>
+          <t>Xalapa</t>
         </is>
       </c>
       <c r="C381">
@@ -5462,9 +7217,14 @@
       </c>
     </row>
     <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>ÁLAMO TEMAPACHE</t>
+          <t>Álamo Temapache</t>
         </is>
       </c>
       <c r="C382">
@@ -5475,9 +7235,14 @@
       </c>
     </row>
     <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C383">
@@ -5490,12 +7255,12 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>YUCATÁN</t>
+          <t>Yucatán</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>MOTUL</t>
+          <t>Motul</t>
         </is>
       </c>
       <c r="C384">
@@ -5506,9 +7271,14 @@
       </c>
     </row>
     <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>MÉRIDA</t>
+          <t>Mérida</t>
         </is>
       </c>
       <c r="C385">
@@ -5519,9 +7289,14 @@
       </c>
     </row>
     <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C386">
@@ -5534,12 +7309,12 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>ZACATECAS</t>
+          <t>Zacatecas</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>FRESNILLO</t>
+          <t>Fresnillo</t>
         </is>
       </c>
       <c r="C387">
@@ -5550,9 +7325,14 @@
       </c>
     </row>
     <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>OJOCALIENTE</t>
+          <t>Ojocaliente</t>
         </is>
       </c>
       <c r="C388">
@@ -5563,9 +7343,14 @@
       </c>
     </row>
     <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>PINOS</t>
+          <t>Pinos</t>
         </is>
       </c>
       <c r="C389">
@@ -5576,9 +7361,14 @@
       </c>
     </row>
     <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>SOMBRERETE</t>
+          <t>Sombrerete</t>
         </is>
       </c>
       <c r="C390">
@@ -5589,9 +7379,14 @@
       </c>
     </row>
     <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>TEÚL DE GONZÁLEZ ORTEGA</t>
+          <t>Teúl De González Ortega</t>
         </is>
       </c>
       <c r="C391">
@@ -5602,9 +7397,14 @@
       </c>
     </row>
     <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C392">
@@ -5617,7 +7417,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C393">
@@ -5625,41 +7425,6 @@
       </c>
       <c r="D393">
         <v>1</v>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 789,030</t>
-        </is>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de Mexicanas y Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>Noviembre de 2024</t>
-        </is>
       </c>
     </row>
   </sheetData>
